--- a/data/PropertyTycoonCardData.xlsx
+++ b/data/PropertyTycoonCardData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gabrielvasile/Documents/Year 2 Uni/Software Engineering/Property_Tycoon_FX/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D78AC4A5-A6E7-F640-8E84-30341C7660FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCBE6370-C25E-944F-AF9C-819F423DB2AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3980" yWindow="760" windowWidth="16060" windowHeight="13660" xr2:uid="{BDE750ED-885A-4E53-AB7E-A47D1E3F79CA}"/>
+    <workbookView xWindow="1720" yWindow="1480" windowWidth="20400" windowHeight="14500" xr2:uid="{BDE750ED-885A-4E53-AB7E-A47D1E3F79CA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,14 +25,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="58">
   <si>
     <t>Property Tycoon board data</t>
   </si>
   <si>
-    <t>Pot luck card data</t>
-  </si>
-  <si>
     <t>Description</t>
   </si>
   <si>
@@ -108,9 +105,6 @@
     <t>Retained by the player until needed. No resale or trade value</t>
   </si>
   <si>
-    <t>Opportunity knocks card data</t>
-  </si>
-  <si>
     <t>"Savings bond matures, collect £100</t>
   </si>
   <si>
@@ -199,6 +193,12 @@
   </si>
   <si>
     <t>Player token moves backwards to the Old Creek</t>
+  </si>
+  <si>
+    <t>Pot Luck data</t>
+  </si>
+  <si>
+    <t>Oportunity Knocks data</t>
   </si>
 </sst>
 </file>
@@ -230,12 +230,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -250,10 +262,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -568,307 +583,532 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{824FCAE1-2E2D-480B-8168-72B223ADDCE7}">
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="41" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="2" t="s">
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+    </row>
+    <row r="5" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A11" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A13" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A15" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A16" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A17" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A18" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A19" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A20" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A21" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>52</v>
-      </c>
-      <c r="D6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>53</v>
-      </c>
-      <c r="D7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A22" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A23" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A24" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A25" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="3"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A26" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="3"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A27" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="3"/>
+      <c r="I27" s="3"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A28" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A29" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="3"/>
+      <c r="I29" s="3"/>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A30" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="3"/>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A31" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3"/>
+      <c r="I31" s="3"/>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A32" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="3"/>
+      <c r="I32" s="3"/>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A33" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3"/>
+      <c r="I33" s="3"/>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A34" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D8" t="s">
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+      <c r="H34" s="3"/>
+      <c r="I34" s="3"/>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A35" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
+      <c r="H35" s="3"/>
+      <c r="I35" s="3"/>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A37" s="4"/>
+      <c r="B37" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A38" s="3"/>
+      <c r="B38" t="s">
         <v>57</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>11</v>
-      </c>
-      <c r="D12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>13</v>
-      </c>
-      <c r="D13" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>15</v>
-      </c>
-      <c r="D14" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>55</v>
-      </c>
-      <c r="D15" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>17</v>
-      </c>
-      <c r="D16" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>19</v>
-      </c>
-      <c r="D17" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>28</v>
-      </c>
-      <c r="D18" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>29</v>
-      </c>
-      <c r="D19" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>45</v>
-      </c>
-      <c r="D20" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>23</v>
-      </c>
-      <c r="D21" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>25</v>
-      </c>
-      <c r="D22" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>30</v>
-      </c>
-      <c r="D27" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>31</v>
-      </c>
-      <c r="D28" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>32</v>
-      </c>
-      <c r="D29" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>46</v>
-      </c>
-      <c r="D30" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>35</v>
-      </c>
-      <c r="D31" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>37</v>
-      </c>
-      <c r="D32" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>47</v>
-      </c>
-      <c r="D33" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>39</v>
-      </c>
-      <c r="D34" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>48</v>
-      </c>
-      <c r="D35" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>42</v>
-      </c>
-      <c r="D36" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
-        <v>49</v>
-      </c>
-      <c r="D37" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
-        <v>43</v>
-      </c>
-      <c r="D38" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
-        <v>50</v>
-      </c>
-      <c r="D39" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
-        <v>29</v>
-      </c>
-      <c r="D40" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
-        <v>56</v>
-      </c>
-      <c r="D41" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
-        <v>25</v>
-      </c>
-      <c r="D42" t="s">
-        <v>26</v>
       </c>
     </row>
   </sheetData>
